--- a/experiment/verification_resultsall9columns.xlsx
+++ b/experiment/verification_resultsall9columns.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZhuoK\Documents\GitHub\ila-webapp\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC92A448-B344-4E8E-85F6-1867D21C205F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702553C7-2F9E-49DE-BBA1-65290C6B9200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E5A255F9-3B15-4293-89FA-12C15929A2DB}"/>
+    <workbookView xWindow="35415" yWindow="2205" windowWidth="21600" windowHeight="11385" xr2:uid="{E5A255F9-3B15-4293-89FA-12C15929A2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="verification_resultsall9columns" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="1803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="1806">
   <si>
     <t>Excel_Row</t>
   </si>
@@ -8196,6 +8183,15 @@
   </si>
   <si>
     <t>Fail % (per 100 students)</t>
+  </si>
+  <si>
+    <t>Percentage of Failures (%)</t>
+  </si>
+  <si>
+    <t>No. of Verdict: FAIL across 100 rows * 9 dimensions</t>
+  </si>
+  <si>
+    <t>out of 900 rows</t>
   </si>
 </sst>
 </file>
@@ -8532,7 +8528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -8662,6 +8658,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -8707,7 +8744,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8719,6 +8756,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -9105,14 +9158,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C017E952-9912-4DB9-A53B-768EB2C569CC}">
   <dimension ref="A1:J901"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9129,7 +9182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -9159,7 +9212,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9185,7 +9238,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -9211,7 +9264,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -9237,7 +9290,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9263,7 +9316,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -9289,7 +9342,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -9315,7 +9368,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -9341,7 +9394,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -9357,17 +9410,17 @@
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="5">
         <v>19</v>
       </c>
       <c r="J10" s="4">
         <v>0.19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -9383,17 +9436,17 @@
       <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="6">
         <v>7</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -9409,12 +9462,18 @@
       <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I12">
+      <c r="H12" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="I12" s="8">
         <f>SUM(I3:I11)</f>
         <v>210</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3</v>
       </c>
@@ -9430,8 +9489,15 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="I13" s="8">
+        <f>210/900*100</f>
+        <v>23.333333333333332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
@@ -9448,7 +9514,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
@@ -9465,7 +9531,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -9482,7 +9548,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
@@ -9499,7 +9565,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
@@ -9516,7 +9582,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -9533,7 +9599,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -9550,7 +9616,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
@@ -9567,7 +9633,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -9584,7 +9650,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4</v>
       </c>
@@ -9601,7 +9667,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4</v>
       </c>
@@ -9618,7 +9684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4</v>
       </c>
@@ -9635,7 +9701,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9652,7 +9718,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -9669,7 +9735,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -9686,7 +9752,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5</v>
       </c>
@@ -9703,7 +9769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9720,7 +9786,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5</v>
       </c>
@@ -9737,7 +9803,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -9754,7 +9820,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -9771,7 +9837,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -9788,7 +9854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -9805,7 +9871,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -9822,7 +9888,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -9839,7 +9905,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -9856,7 +9922,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -9873,7 +9939,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -9890,7 +9956,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6</v>
       </c>
@@ -9907,7 +9973,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>6</v>
       </c>
@@ -9924,7 +9990,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -9941,7 +10007,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>6</v>
       </c>
@@ -9958,7 +10024,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>6</v>
       </c>
@@ -9975,7 +10041,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>6</v>
       </c>
@@ -9992,7 +10058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>7</v>
       </c>
@@ -10009,7 +10075,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>7</v>
       </c>
@@ -10026,7 +10092,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>7</v>
       </c>
@@ -10043,7 +10109,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>7</v>
       </c>
@@ -10060,7 +10126,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>7</v>
       </c>
@@ -10077,7 +10143,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>7</v>
       </c>
@@ -10094,7 +10160,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>7</v>
       </c>
@@ -10111,7 +10177,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>7</v>
       </c>
@@ -10128,7 +10194,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>7</v>
       </c>
@@ -10145,7 +10211,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>8</v>
       </c>
@@ -10162,7 +10228,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8</v>
       </c>
@@ -10179,7 +10245,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>8</v>
       </c>
@@ -10196,7 +10262,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>8</v>
       </c>
@@ -10213,7 +10279,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>8</v>
       </c>
@@ -10230,7 +10296,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>8</v>
       </c>
@@ -10247,7 +10313,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>8</v>
       </c>
@@ -10264,7 +10330,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>8</v>
       </c>
@@ -10281,7 +10347,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>8</v>
       </c>
@@ -10298,7 +10364,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>9</v>
       </c>
@@ -10315,7 +10381,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>9</v>
       </c>
@@ -10332,7 +10398,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>9</v>
       </c>
@@ -10349,7 +10415,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>9</v>
       </c>
@@ -10366,7 +10432,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>9</v>
       </c>
@@ -10383,7 +10449,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9</v>
       </c>
@@ -10400,7 +10466,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>9</v>
       </c>
@@ -10417,7 +10483,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>9</v>
       </c>
@@ -10434,7 +10500,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>9</v>
       </c>
@@ -10451,7 +10517,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10</v>
       </c>
@@ -10468,7 +10534,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10</v>
       </c>
@@ -10485,7 +10551,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>10</v>
       </c>
@@ -10502,7 +10568,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>10</v>
       </c>
@@ -10519,7 +10585,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>10</v>
       </c>
@@ -10536,7 +10602,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>10</v>
       </c>
@@ -10553,7 +10619,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>10</v>
       </c>
@@ -10570,7 +10636,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>10</v>
       </c>
@@ -10587,7 +10653,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>10</v>
       </c>
@@ -10604,7 +10670,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>11</v>
       </c>
@@ -10621,7 +10687,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>11</v>
       </c>
@@ -10638,7 +10704,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>11</v>
       </c>
@@ -10655,7 +10721,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>11</v>
       </c>
@@ -10672,7 +10738,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>11</v>
       </c>
@@ -10689,7 +10755,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>11</v>
       </c>
@@ -10706,7 +10772,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>11</v>
       </c>
@@ -10723,7 +10789,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>11</v>
       </c>
@@ -10740,7 +10806,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>11</v>
       </c>
@@ -10757,7 +10823,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>12</v>
       </c>
@@ -10774,7 +10840,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>12</v>
       </c>
@@ -10791,7 +10857,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>12</v>
       </c>
@@ -10808,7 +10874,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>12</v>
       </c>
@@ -10825,7 +10891,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>12</v>
       </c>
@@ -10842,7 +10908,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>12</v>
       </c>
@@ -10859,7 +10925,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>12</v>
       </c>
@@ -10876,7 +10942,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>12</v>
       </c>
@@ -10893,7 +10959,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>12</v>
       </c>
@@ -10910,7 +10976,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>13</v>
       </c>
@@ -10927,7 +10993,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>13</v>
       </c>
@@ -10944,7 +11010,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>13</v>
       </c>
@@ -10961,7 +11027,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>13</v>
       </c>
@@ -10978,7 +11044,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>13</v>
       </c>
@@ -10995,7 +11061,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>13</v>
       </c>
@@ -11012,7 +11078,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>13</v>
       </c>
@@ -11029,7 +11095,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>13</v>
       </c>
@@ -11046,7 +11112,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>13</v>
       </c>
@@ -11063,7 +11129,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>14</v>
       </c>
@@ -11080,7 +11146,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>14</v>
       </c>
@@ -11097,7 +11163,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>14</v>
       </c>
@@ -11114,7 +11180,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>14</v>
       </c>
@@ -11131,7 +11197,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>14</v>
       </c>
@@ -11148,7 +11214,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>14</v>
       </c>
@@ -11165,7 +11231,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>14</v>
       </c>
@@ -11182,7 +11248,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>14</v>
       </c>
@@ -11199,7 +11265,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>14</v>
       </c>
@@ -11216,7 +11282,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>15</v>
       </c>
@@ -11233,7 +11299,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>15</v>
       </c>
@@ -11250,7 +11316,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>15</v>
       </c>
@@ -11267,7 +11333,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>15</v>
       </c>
@@ -11284,7 +11350,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>15</v>
       </c>
@@ -11301,7 +11367,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>15</v>
       </c>
@@ -11318,7 +11384,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>15</v>
       </c>
@@ -11335,7 +11401,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>15</v>
       </c>
@@ -11352,7 +11418,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>15</v>
       </c>
@@ -11369,7 +11435,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>16</v>
       </c>
@@ -11386,7 +11452,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>16</v>
       </c>
@@ -11403,7 +11469,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>16</v>
       </c>
@@ -11420,7 +11486,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>16</v>
       </c>
@@ -11437,7 +11503,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>16</v>
       </c>
@@ -11454,7 +11520,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>16</v>
       </c>
@@ -11471,7 +11537,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>16</v>
       </c>
@@ -11488,7 +11554,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>16</v>
       </c>
@@ -11505,7 +11571,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>16</v>
       </c>
@@ -11522,7 +11588,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>17</v>
       </c>
@@ -11539,7 +11605,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>17</v>
       </c>
@@ -11556,7 +11622,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>17</v>
       </c>
@@ -11573,7 +11639,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>17</v>
       </c>
@@ -11590,7 +11656,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>17</v>
       </c>
@@ -11607,7 +11673,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>17</v>
       </c>
@@ -11624,7 +11690,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>17</v>
       </c>
@@ -11641,7 +11707,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>17</v>
       </c>
@@ -11658,7 +11724,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>17</v>
       </c>
@@ -11675,7 +11741,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>18</v>
       </c>
@@ -11692,7 +11758,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>18</v>
       </c>
@@ -11709,7 +11775,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>18</v>
       </c>
@@ -11726,7 +11792,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>18</v>
       </c>
@@ -11743,7 +11809,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>18</v>
       </c>
@@ -11760,7 +11826,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>18</v>
       </c>
@@ -11777,7 +11843,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>18</v>
       </c>
@@ -11794,7 +11860,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>18</v>
       </c>
@@ -11811,7 +11877,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>18</v>
       </c>
@@ -11828,7 +11894,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>19</v>
       </c>
@@ -11845,7 +11911,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>19</v>
       </c>
@@ -11862,7 +11928,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>19</v>
       </c>
@@ -11879,7 +11945,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>19</v>
       </c>
@@ -11896,7 +11962,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>19</v>
       </c>
@@ -11913,7 +11979,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>19</v>
       </c>
@@ -11930,7 +11996,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>19</v>
       </c>
@@ -11947,7 +12013,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>19</v>
       </c>
@@ -11964,7 +12030,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>19</v>
       </c>
@@ -11981,7 +12047,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>20</v>
       </c>
@@ -11998,7 +12064,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>20</v>
       </c>
@@ -12015,7 +12081,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>20</v>
       </c>
@@ -12032,7 +12098,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>20</v>
       </c>
@@ -12049,7 +12115,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>20</v>
       </c>
@@ -12066,7 +12132,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>20</v>
       </c>
@@ -12083,7 +12149,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>20</v>
       </c>
@@ -12100,7 +12166,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>20</v>
       </c>
@@ -12117,7 +12183,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>20</v>
       </c>
@@ -12134,7 +12200,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>21</v>
       </c>
@@ -12151,7 +12217,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>21</v>
       </c>
@@ -12168,7 +12234,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>21</v>
       </c>
@@ -12185,7 +12251,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>21</v>
       </c>
@@ -12202,7 +12268,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>21</v>
       </c>
@@ -12219,7 +12285,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>21</v>
       </c>
@@ -12236,7 +12302,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>21</v>
       </c>
@@ -12253,7 +12319,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>21</v>
       </c>
@@ -12270,7 +12336,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>21</v>
       </c>
@@ -12287,7 +12353,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>22</v>
       </c>
@@ -12304,7 +12370,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>22</v>
       </c>
@@ -12321,7 +12387,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>22</v>
       </c>
@@ -12338,7 +12404,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>22</v>
       </c>
@@ -12355,7 +12421,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>22</v>
       </c>
@@ -12372,7 +12438,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>22</v>
       </c>
@@ -12389,7 +12455,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>22</v>
       </c>
@@ -12406,7 +12472,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>22</v>
       </c>
@@ -12423,7 +12489,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>22</v>
       </c>
@@ -12440,7 +12506,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>23</v>
       </c>
@@ -12457,7 +12523,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>23</v>
       </c>
@@ -12474,7 +12540,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>23</v>
       </c>
@@ -12491,7 +12557,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>23</v>
       </c>
@@ -12508,7 +12574,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>23</v>
       </c>
@@ -12525,7 +12591,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>23</v>
       </c>
@@ -12542,7 +12608,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>23</v>
       </c>
@@ -12559,7 +12625,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>23</v>
       </c>
@@ -12576,7 +12642,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>23</v>
       </c>
@@ -12593,7 +12659,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>24</v>
       </c>
@@ -12610,7 +12676,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>24</v>
       </c>
@@ -12627,7 +12693,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>24</v>
       </c>
@@ -12644,7 +12710,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>24</v>
       </c>
@@ -12661,7 +12727,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>24</v>
       </c>
@@ -12678,7 +12744,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>24</v>
       </c>
@@ -12695,7 +12761,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>24</v>
       </c>
@@ -12712,7 +12778,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>24</v>
       </c>
@@ -12729,7 +12795,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>24</v>
       </c>
@@ -12746,7 +12812,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>25</v>
       </c>
@@ -12763,7 +12829,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>25</v>
       </c>
@@ -12780,7 +12846,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>25</v>
       </c>
@@ -12797,7 +12863,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>25</v>
       </c>
@@ -12814,7 +12880,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>25</v>
       </c>
@@ -12831,7 +12897,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>25</v>
       </c>
@@ -12848,7 +12914,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>25</v>
       </c>
@@ -12865,7 +12931,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>25</v>
       </c>
@@ -12882,7 +12948,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>25</v>
       </c>
@@ -12899,7 +12965,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>26</v>
       </c>
@@ -12916,7 +12982,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>26</v>
       </c>
@@ -12933,7 +12999,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>26</v>
       </c>
@@ -12950,7 +13016,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>26</v>
       </c>
@@ -12967,7 +13033,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>26</v>
       </c>
@@ -12984,7 +13050,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>26</v>
       </c>
@@ -13001,7 +13067,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>26</v>
       </c>
@@ -13018,7 +13084,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>26</v>
       </c>
@@ -13035,7 +13101,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>26</v>
       </c>
@@ -13052,7 +13118,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>27</v>
       </c>
@@ -13069,7 +13135,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>27</v>
       </c>
@@ -13086,7 +13152,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>27</v>
       </c>
@@ -13103,7 +13169,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>27</v>
       </c>
@@ -13120,7 +13186,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>27</v>
       </c>
@@ -13137,7 +13203,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>27</v>
       </c>
@@ -13154,7 +13220,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>27</v>
       </c>
@@ -13171,7 +13237,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>27</v>
       </c>
@@ -13188,7 +13254,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>27</v>
       </c>
@@ -13205,7 +13271,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>28</v>
       </c>
@@ -13222,7 +13288,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>28</v>
       </c>
@@ -13239,7 +13305,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>28</v>
       </c>
@@ -13256,7 +13322,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>28</v>
       </c>
@@ -13273,7 +13339,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>28</v>
       </c>
@@ -13290,7 +13356,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>28</v>
       </c>
@@ -13307,7 +13373,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>28</v>
       </c>
@@ -13324,7 +13390,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>28</v>
       </c>
@@ -13341,7 +13407,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>28</v>
       </c>
@@ -13358,7 +13424,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>29</v>
       </c>
@@ -13375,7 +13441,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>29</v>
       </c>
@@ -13392,7 +13458,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>29</v>
       </c>
@@ -13409,7 +13475,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>29</v>
       </c>
@@ -13426,7 +13492,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>29</v>
       </c>
@@ -13443,7 +13509,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>29</v>
       </c>
@@ -13460,7 +13526,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>29</v>
       </c>
@@ -13477,7 +13543,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>29</v>
       </c>
@@ -13494,7 +13560,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>29</v>
       </c>
@@ -13511,7 +13577,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>30</v>
       </c>
@@ -13528,7 +13594,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>30</v>
       </c>
@@ -13545,7 +13611,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>30</v>
       </c>
@@ -13562,7 +13628,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>30</v>
       </c>
@@ -13579,7 +13645,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>30</v>
       </c>
@@ -13596,7 +13662,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>30</v>
       </c>
@@ -13613,7 +13679,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>30</v>
       </c>
@@ -13630,7 +13696,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>30</v>
       </c>
@@ -13647,7 +13713,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>30</v>
       </c>
@@ -13664,7 +13730,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>31</v>
       </c>
@@ -13681,7 +13747,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>31</v>
       </c>
@@ -13698,7 +13764,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>31</v>
       </c>
@@ -13715,7 +13781,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>31</v>
       </c>
@@ -13732,7 +13798,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>31</v>
       </c>
@@ -13749,7 +13815,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>31</v>
       </c>
@@ -13766,7 +13832,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>31</v>
       </c>
@@ -13783,7 +13849,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>31</v>
       </c>
@@ -13800,7 +13866,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>31</v>
       </c>
@@ -13817,7 +13883,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>32</v>
       </c>
@@ -13834,7 +13900,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>32</v>
       </c>
@@ -13851,7 +13917,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>32</v>
       </c>
@@ -13868,7 +13934,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>32</v>
       </c>
@@ -13885,7 +13951,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>32</v>
       </c>
@@ -13902,7 +13968,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>32</v>
       </c>
@@ -13919,7 +13985,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>32</v>
       </c>
@@ -13936,7 +14002,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>32</v>
       </c>
@@ -13953,7 +14019,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>32</v>
       </c>
@@ -13970,7 +14036,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>33</v>
       </c>
@@ -13987,7 +14053,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>33</v>
       </c>
@@ -14004,7 +14070,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>33</v>
       </c>
@@ -14021,7 +14087,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>33</v>
       </c>
@@ -14038,7 +14104,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>33</v>
       </c>
@@ -14055,7 +14121,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>33</v>
       </c>
@@ -14072,7 +14138,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>33</v>
       </c>
@@ -14089,7 +14155,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>33</v>
       </c>
@@ -14106,7 +14172,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>33</v>
       </c>
@@ -14123,7 +14189,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>34</v>
       </c>
@@ -14140,7 +14206,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>34</v>
       </c>
@@ -14157,7 +14223,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>34</v>
       </c>
@@ -14174,7 +14240,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>34</v>
       </c>
@@ -14191,7 +14257,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>34</v>
       </c>
@@ -14208,7 +14274,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>34</v>
       </c>
@@ -14225,7 +14291,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>34</v>
       </c>
@@ -14242,7 +14308,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>34</v>
       </c>
@@ -14259,7 +14325,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>34</v>
       </c>
@@ -14276,7 +14342,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>35</v>
       </c>
@@ -14293,7 +14359,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>35</v>
       </c>
@@ -14310,7 +14376,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>35</v>
       </c>
@@ -14327,7 +14393,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>35</v>
       </c>
@@ -14344,7 +14410,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>35</v>
       </c>
@@ -14361,7 +14427,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>35</v>
       </c>
@@ -14378,7 +14444,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>35</v>
       </c>
@@ -14395,7 +14461,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>35</v>
       </c>
@@ -14412,7 +14478,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>35</v>
       </c>
@@ -14429,7 +14495,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>36</v>
       </c>
@@ -14446,7 +14512,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>36</v>
       </c>
@@ -14463,7 +14529,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>36</v>
       </c>
@@ -14480,7 +14546,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>36</v>
       </c>
@@ -14497,7 +14563,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>36</v>
       </c>
@@ -14514,7 +14580,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>36</v>
       </c>
@@ -14531,7 +14597,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>36</v>
       </c>
@@ -14548,7 +14614,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>36</v>
       </c>
@@ -14565,7 +14631,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>36</v>
       </c>
@@ -14582,7 +14648,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>37</v>
       </c>
@@ -14599,7 +14665,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>37</v>
       </c>
@@ -14616,7 +14682,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>37</v>
       </c>
@@ -14633,7 +14699,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>37</v>
       </c>
@@ -14650,7 +14716,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>37</v>
       </c>
@@ -14667,7 +14733,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>37</v>
       </c>
@@ -14684,7 +14750,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>37</v>
       </c>
@@ -14701,7 +14767,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>37</v>
       </c>
@@ -14718,7 +14784,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>37</v>
       </c>
@@ -14735,7 +14801,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>38</v>
       </c>
@@ -14752,7 +14818,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>38</v>
       </c>
@@ -14769,7 +14835,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>38</v>
       </c>
@@ -14786,7 +14852,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>38</v>
       </c>
@@ -14803,7 +14869,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>38</v>
       </c>
@@ -14820,7 +14886,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>38</v>
       </c>
@@ -14837,7 +14903,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>38</v>
       </c>
@@ -14854,7 +14920,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>38</v>
       </c>
@@ -14871,7 +14937,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>38</v>
       </c>
@@ -14888,7 +14954,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>39</v>
       </c>
@@ -14905,7 +14971,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>39</v>
       </c>
@@ -14922,7 +14988,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>39</v>
       </c>
@@ -14939,7 +15005,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>39</v>
       </c>
@@ -14956,7 +15022,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>39</v>
       </c>
@@ -14973,7 +15039,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>39</v>
       </c>
@@ -14990,7 +15056,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>39</v>
       </c>
@@ -15007,7 +15073,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>39</v>
       </c>
@@ -15024,7 +15090,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>39</v>
       </c>
@@ -15041,7 +15107,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>40</v>
       </c>
@@ -15058,7 +15124,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>40</v>
       </c>
@@ -15075,7 +15141,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>40</v>
       </c>
@@ -15092,7 +15158,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>40</v>
       </c>
@@ -15109,7 +15175,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>40</v>
       </c>
@@ -15126,7 +15192,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>40</v>
       </c>
@@ -15143,7 +15209,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>40</v>
       </c>
@@ -15160,7 +15226,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>40</v>
       </c>
@@ -15177,7 +15243,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>40</v>
       </c>
@@ -15194,7 +15260,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>41</v>
       </c>
@@ -15211,7 +15277,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>41</v>
       </c>
@@ -15228,7 +15294,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>41</v>
       </c>
@@ -15245,7 +15311,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>41</v>
       </c>
@@ -15262,7 +15328,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>41</v>
       </c>
@@ -15279,7 +15345,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>41</v>
       </c>
@@ -15296,7 +15362,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>41</v>
       </c>
@@ -15313,7 +15379,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>41</v>
       </c>
@@ -15330,7 +15396,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>41</v>
       </c>
@@ -15347,7 +15413,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>42</v>
       </c>
@@ -15364,7 +15430,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>42</v>
       </c>
@@ -15381,7 +15447,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>42</v>
       </c>
@@ -15398,7 +15464,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>42</v>
       </c>
@@ -15415,7 +15481,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>42</v>
       </c>
@@ -15432,7 +15498,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>42</v>
       </c>
@@ -15449,7 +15515,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>42</v>
       </c>
@@ -15466,7 +15532,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>42</v>
       </c>
@@ -15483,7 +15549,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>42</v>
       </c>
@@ -15500,7 +15566,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>43</v>
       </c>
@@ -15517,7 +15583,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>43</v>
       </c>
@@ -15534,7 +15600,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>43</v>
       </c>
@@ -15551,7 +15617,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>43</v>
       </c>
@@ -15568,7 +15634,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>43</v>
       </c>
@@ -15585,7 +15651,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>43</v>
       </c>
@@ -15602,7 +15668,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>43</v>
       </c>
@@ -15619,7 +15685,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>43</v>
       </c>
@@ -15636,7 +15702,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>43</v>
       </c>
@@ -15653,7 +15719,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>44</v>
       </c>
@@ -15670,7 +15736,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>44</v>
       </c>
@@ -15687,7 +15753,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>44</v>
       </c>
@@ -15704,7 +15770,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>44</v>
       </c>
@@ -15721,7 +15787,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>44</v>
       </c>
@@ -15738,7 +15804,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>44</v>
       </c>
@@ -15755,7 +15821,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>44</v>
       </c>
@@ -15772,7 +15838,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>44</v>
       </c>
@@ -15789,7 +15855,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>44</v>
       </c>
@@ -15806,7 +15872,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>45</v>
       </c>
@@ -15823,7 +15889,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>45</v>
       </c>
@@ -15840,7 +15906,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>45</v>
       </c>
@@ -15857,7 +15923,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>45</v>
       </c>
@@ -15874,7 +15940,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>45</v>
       </c>
@@ -15891,7 +15957,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>45</v>
       </c>
@@ -15908,7 +15974,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>45</v>
       </c>
@@ -15925,7 +15991,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>45</v>
       </c>
@@ -15942,7 +16008,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>45</v>
       </c>
@@ -15959,7 +16025,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>46</v>
       </c>
@@ -15976,7 +16042,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>46</v>
       </c>
@@ -15993,7 +16059,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>46</v>
       </c>
@@ -16010,7 +16076,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>46</v>
       </c>
@@ -16027,7 +16093,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>46</v>
       </c>
@@ -16044,7 +16110,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>46</v>
       </c>
@@ -16061,7 +16127,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>46</v>
       </c>
@@ -16078,7 +16144,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>46</v>
       </c>
@@ -16095,7 +16161,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>46</v>
       </c>
@@ -16112,7 +16178,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>47</v>
       </c>
@@ -16129,7 +16195,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>47</v>
       </c>
@@ -16146,7 +16212,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>47</v>
       </c>
@@ -16163,7 +16229,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>47</v>
       </c>
@@ -16180,7 +16246,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>47</v>
       </c>
@@ -16197,7 +16263,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>47</v>
       </c>
@@ -16214,7 +16280,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>47</v>
       </c>
@@ -16231,7 +16297,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>47</v>
       </c>
@@ -16248,7 +16314,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>47</v>
       </c>
@@ -16265,7 +16331,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>48</v>
       </c>
@@ -16282,7 +16348,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>48</v>
       </c>
@@ -16299,7 +16365,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>48</v>
       </c>
@@ -16316,7 +16382,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>48</v>
       </c>
@@ -16333,7 +16399,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>48</v>
       </c>
@@ -16350,7 +16416,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>48</v>
       </c>
@@ -16367,7 +16433,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>48</v>
       </c>
@@ -16384,7 +16450,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>48</v>
       </c>
@@ -16401,7 +16467,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>48</v>
       </c>
@@ -16418,7 +16484,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>49</v>
       </c>
@@ -16435,7 +16501,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>49</v>
       </c>
@@ -16452,7 +16518,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>49</v>
       </c>
@@ -16469,7 +16535,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>49</v>
       </c>
@@ -16486,7 +16552,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>49</v>
       </c>
@@ -16503,7 +16569,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>49</v>
       </c>
@@ -16520,7 +16586,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>49</v>
       </c>
@@ -16537,7 +16603,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>49</v>
       </c>
@@ -16554,7 +16620,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>49</v>
       </c>
@@ -16571,7 +16637,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>50</v>
       </c>
@@ -16588,7 +16654,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>50</v>
       </c>
@@ -16605,7 +16671,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>50</v>
       </c>
@@ -16622,7 +16688,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>50</v>
       </c>
@@ -16639,7 +16705,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>50</v>
       </c>
@@ -16656,7 +16722,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>50</v>
       </c>
@@ -16673,7 +16739,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>50</v>
       </c>
@@ -16690,7 +16756,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>50</v>
       </c>
@@ -16707,7 +16773,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>50</v>
       </c>
@@ -16724,7 +16790,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>51</v>
       </c>
@@ -16741,7 +16807,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>51</v>
       </c>
@@ -16758,7 +16824,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>51</v>
       </c>
@@ -16775,7 +16841,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>51</v>
       </c>
@@ -16792,7 +16858,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>51</v>
       </c>
@@ -16809,7 +16875,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>51</v>
       </c>
@@ -16826,7 +16892,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>51</v>
       </c>
@@ -16843,7 +16909,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>51</v>
       </c>
@@ -16860,7 +16926,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>51</v>
       </c>
@@ -16877,7 +16943,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>52</v>
       </c>
@@ -16894,7 +16960,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>52</v>
       </c>
@@ -16911,7 +16977,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>52</v>
       </c>
@@ -16928,7 +16994,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>52</v>
       </c>
@@ -16945,7 +17011,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>52</v>
       </c>
@@ -16962,7 +17028,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>52</v>
       </c>
@@ -16979,7 +17045,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>52</v>
       </c>
@@ -16996,7 +17062,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>52</v>
       </c>
@@ -17013,7 +17079,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>52</v>
       </c>
@@ -17030,7 +17096,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>53</v>
       </c>
@@ -17047,7 +17113,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>53</v>
       </c>
@@ -17064,7 +17130,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>53</v>
       </c>
@@ -17081,7 +17147,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>53</v>
       </c>
@@ -17098,7 +17164,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>53</v>
       </c>
@@ -17115,7 +17181,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>53</v>
       </c>
@@ -17132,7 +17198,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>53</v>
       </c>
@@ -17149,7 +17215,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>53</v>
       </c>
@@ -17166,7 +17232,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>53</v>
       </c>
@@ -17183,7 +17249,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>54</v>
       </c>
@@ -17200,7 +17266,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>54</v>
       </c>
@@ -17217,7 +17283,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>54</v>
       </c>
@@ -17234,7 +17300,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>54</v>
       </c>
@@ -17251,7 +17317,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>54</v>
       </c>
@@ -17268,7 +17334,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>54</v>
       </c>
@@ -17285,7 +17351,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>54</v>
       </c>
@@ -17302,7 +17368,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>54</v>
       </c>
@@ -17319,7 +17385,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>54</v>
       </c>
@@ -17336,7 +17402,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>55</v>
       </c>
@@ -17353,7 +17419,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>55</v>
       </c>
@@ -17370,7 +17436,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>55</v>
       </c>
@@ -17387,7 +17453,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>55</v>
       </c>
@@ -17404,7 +17470,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>55</v>
       </c>
@@ -17421,7 +17487,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>55</v>
       </c>
@@ -17438,7 +17504,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>55</v>
       </c>
@@ -17455,7 +17521,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>55</v>
       </c>
@@ -17472,7 +17538,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>55</v>
       </c>
@@ -17489,7 +17555,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>56</v>
       </c>
@@ -17506,7 +17572,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>56</v>
       </c>
@@ -17523,7 +17589,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>56</v>
       </c>
@@ -17540,7 +17606,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>56</v>
       </c>
@@ -17557,7 +17623,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>56</v>
       </c>
@@ -17574,7 +17640,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>56</v>
       </c>
@@ -17591,7 +17657,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>56</v>
       </c>
@@ -17608,7 +17674,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>56</v>
       </c>
@@ -17625,7 +17691,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>56</v>
       </c>
@@ -17642,7 +17708,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>57</v>
       </c>
@@ -17659,7 +17725,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>57</v>
       </c>
@@ -17676,7 +17742,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>57</v>
       </c>
@@ -17693,7 +17759,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>57</v>
       </c>
@@ -17710,7 +17776,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>57</v>
       </c>
@@ -17727,7 +17793,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>57</v>
       </c>
@@ -17744,7 +17810,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>57</v>
       </c>
@@ -17761,7 +17827,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>57</v>
       </c>
@@ -17778,7 +17844,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>57</v>
       </c>
@@ -17795,7 +17861,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>58</v>
       </c>
@@ -17812,7 +17878,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>58</v>
       </c>
@@ -17829,7 +17895,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>58</v>
       </c>
@@ -17846,7 +17912,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>58</v>
       </c>
@@ -17863,7 +17929,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>58</v>
       </c>
@@ -17880,7 +17946,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>58</v>
       </c>
@@ -17897,7 +17963,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>58</v>
       </c>
@@ -17914,7 +17980,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>58</v>
       </c>
@@ -17931,7 +17997,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>58</v>
       </c>
@@ -17948,7 +18014,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>59</v>
       </c>
@@ -17965,7 +18031,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>59</v>
       </c>
@@ -17982,7 +18048,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>59</v>
       </c>
@@ -17999,7 +18065,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>59</v>
       </c>
@@ -18016,7 +18082,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>59</v>
       </c>
@@ -18033,7 +18099,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>59</v>
       </c>
@@ -18050,7 +18116,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>59</v>
       </c>
@@ -18067,7 +18133,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>59</v>
       </c>
@@ -18084,7 +18150,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>59</v>
       </c>
@@ -18101,7 +18167,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>60</v>
       </c>
@@ -18118,7 +18184,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>60</v>
       </c>
@@ -18135,7 +18201,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>60</v>
       </c>
@@ -18152,7 +18218,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>60</v>
       </c>
@@ -18169,7 +18235,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>60</v>
       </c>
@@ -18186,7 +18252,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>60</v>
       </c>
@@ -18203,7 +18269,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>60</v>
       </c>
@@ -18220,7 +18286,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>60</v>
       </c>
@@ -18237,7 +18303,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>60</v>
       </c>
@@ -18254,7 +18320,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>61</v>
       </c>
@@ -18271,7 +18337,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>61</v>
       </c>
@@ -18288,7 +18354,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>61</v>
       </c>
@@ -18305,7 +18371,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>61</v>
       </c>
@@ -18322,7 +18388,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>61</v>
       </c>
@@ -18339,7 +18405,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>61</v>
       </c>
@@ -18356,7 +18422,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>61</v>
       </c>
@@ -18373,7 +18439,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>61</v>
       </c>
@@ -18390,7 +18456,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>61</v>
       </c>
@@ -18407,7 +18473,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>62</v>
       </c>
@@ -18424,7 +18490,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>62</v>
       </c>
@@ -18441,7 +18507,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>62</v>
       </c>
@@ -18458,7 +18524,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>62</v>
       </c>
@@ -18475,7 +18541,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>62</v>
       </c>
@@ -18492,7 +18558,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>62</v>
       </c>
@@ -18509,7 +18575,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>62</v>
       </c>
@@ -18526,7 +18592,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>62</v>
       </c>
@@ -18543,7 +18609,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>62</v>
       </c>
@@ -18560,7 +18626,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>63</v>
       </c>
@@ -18577,7 +18643,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>63</v>
       </c>
@@ -18594,7 +18660,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>63</v>
       </c>
@@ -18611,7 +18677,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>63</v>
       </c>
@@ -18628,7 +18694,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>63</v>
       </c>
@@ -18645,7 +18711,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>63</v>
       </c>
@@ -18662,7 +18728,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>63</v>
       </c>
@@ -18679,7 +18745,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>63</v>
       </c>
@@ -18696,7 +18762,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>63</v>
       </c>
@@ -18713,7 +18779,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>64</v>
       </c>
@@ -18730,7 +18796,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>64</v>
       </c>
@@ -18747,7 +18813,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>64</v>
       </c>
@@ -18764,7 +18830,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>64</v>
       </c>
@@ -18781,7 +18847,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>64</v>
       </c>
@@ -18798,7 +18864,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>64</v>
       </c>
@@ -18815,7 +18881,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>64</v>
       </c>
@@ -18832,7 +18898,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>64</v>
       </c>
@@ -18849,7 +18915,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>64</v>
       </c>
@@ -18866,7 +18932,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>65</v>
       </c>
@@ -18883,7 +18949,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>65</v>
       </c>
@@ -18900,7 +18966,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>65</v>
       </c>
@@ -18917,7 +18983,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>65</v>
       </c>
@@ -18934,7 +19000,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>65</v>
       </c>
@@ -18951,7 +19017,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>65</v>
       </c>
@@ -18968,7 +19034,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>65</v>
       </c>
@@ -18985,7 +19051,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>65</v>
       </c>
@@ -19002,7 +19068,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>65</v>
       </c>
@@ -19019,7 +19085,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>66</v>
       </c>
@@ -19036,7 +19102,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>66</v>
       </c>
@@ -19053,7 +19119,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>66</v>
       </c>
@@ -19070,7 +19136,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>66</v>
       </c>
@@ -19087,7 +19153,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>66</v>
       </c>
@@ -19104,7 +19170,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>66</v>
       </c>
@@ -19121,7 +19187,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>66</v>
       </c>
@@ -19138,7 +19204,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>66</v>
       </c>
@@ -19155,7 +19221,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>66</v>
       </c>
@@ -19172,7 +19238,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>67</v>
       </c>
@@ -19189,7 +19255,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>67</v>
       </c>
@@ -19206,7 +19272,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>67</v>
       </c>
@@ -19223,7 +19289,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>67</v>
       </c>
@@ -19240,7 +19306,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>67</v>
       </c>
@@ -19257,7 +19323,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>67</v>
       </c>
@@ -19274,7 +19340,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>67</v>
       </c>
@@ -19291,7 +19357,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>67</v>
       </c>
@@ -19308,7 +19374,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>67</v>
       </c>
@@ -19325,7 +19391,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>68</v>
       </c>
@@ -19342,7 +19408,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>68</v>
       </c>
@@ -19359,7 +19425,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>68</v>
       </c>
@@ -19376,7 +19442,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>68</v>
       </c>
@@ -19393,7 +19459,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>68</v>
       </c>
@@ -19410,7 +19476,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>68</v>
       </c>
@@ -19427,7 +19493,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>68</v>
       </c>
@@ -19444,7 +19510,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>68</v>
       </c>
@@ -19461,7 +19527,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>68</v>
       </c>
@@ -19478,7 +19544,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>69</v>
       </c>
@@ -19495,7 +19561,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>69</v>
       </c>
@@ -19512,7 +19578,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>69</v>
       </c>
@@ -19529,7 +19595,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>69</v>
       </c>
@@ -19546,7 +19612,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>69</v>
       </c>
@@ -19563,7 +19629,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>69</v>
       </c>
@@ -19580,7 +19646,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>69</v>
       </c>
@@ -19597,7 +19663,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>69</v>
       </c>
@@ -19614,7 +19680,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>69</v>
       </c>
@@ -19631,7 +19697,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>70</v>
       </c>
@@ -19648,7 +19714,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>70</v>
       </c>
@@ -19665,7 +19731,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>70</v>
       </c>
@@ -19682,7 +19748,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>70</v>
       </c>
@@ -19699,7 +19765,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>70</v>
       </c>
@@ -19716,7 +19782,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>70</v>
       </c>
@@ -19733,7 +19799,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>70</v>
       </c>
@@ -19750,7 +19816,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>70</v>
       </c>
@@ -19767,7 +19833,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>70</v>
       </c>
@@ -19784,7 +19850,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>71</v>
       </c>
@@ -19801,7 +19867,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>71</v>
       </c>
@@ -19818,7 +19884,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>71</v>
       </c>
@@ -19835,7 +19901,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>71</v>
       </c>
@@ -19852,7 +19918,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>71</v>
       </c>
@@ -19869,7 +19935,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>71</v>
       </c>
@@ -19886,7 +19952,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>71</v>
       </c>
@@ -19903,7 +19969,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>71</v>
       </c>
@@ -19920,7 +19986,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>71</v>
       </c>
@@ -19937,7 +20003,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>72</v>
       </c>
@@ -19954,7 +20020,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>72</v>
       </c>
@@ -19971,7 +20037,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>72</v>
       </c>
@@ -19988,7 +20054,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>72</v>
       </c>
@@ -20005,7 +20071,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>72</v>
       </c>
@@ -20022,7 +20088,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>72</v>
       </c>
@@ -20039,7 +20105,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>72</v>
       </c>
@@ -20056,7 +20122,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>72</v>
       </c>
@@ -20073,7 +20139,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>72</v>
       </c>
@@ -20090,7 +20156,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>73</v>
       </c>
@@ -20107,7 +20173,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>73</v>
       </c>
@@ -20124,7 +20190,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>73</v>
       </c>
@@ -20141,7 +20207,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>73</v>
       </c>
@@ -20158,7 +20224,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>73</v>
       </c>
@@ -20175,7 +20241,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>73</v>
       </c>
@@ -20192,7 +20258,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>73</v>
       </c>
@@ -20209,7 +20275,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>73</v>
       </c>
@@ -20226,7 +20292,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>73</v>
       </c>
@@ -20243,7 +20309,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>74</v>
       </c>
@@ -20260,7 +20326,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>74</v>
       </c>
@@ -20277,7 +20343,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>74</v>
       </c>
@@ -20294,7 +20360,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>74</v>
       </c>
@@ -20311,7 +20377,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>74</v>
       </c>
@@ -20328,7 +20394,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>74</v>
       </c>
@@ -20345,7 +20411,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>74</v>
       </c>
@@ -20362,7 +20428,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>74</v>
       </c>
@@ -20379,7 +20445,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>74</v>
       </c>
@@ -20396,7 +20462,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>75</v>
       </c>
@@ -20413,7 +20479,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>75</v>
       </c>
@@ -20430,7 +20496,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>75</v>
       </c>
@@ -20447,7 +20513,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>75</v>
       </c>
@@ -20464,7 +20530,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>75</v>
       </c>
@@ -20481,7 +20547,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>75</v>
       </c>
@@ -20498,7 +20564,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>75</v>
       </c>
@@ -20515,7 +20581,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>75</v>
       </c>
@@ -20532,7 +20598,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>75</v>
       </c>
@@ -20549,7 +20615,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>76</v>
       </c>
@@ -20566,7 +20632,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>76</v>
       </c>
@@ -20583,7 +20649,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>76</v>
       </c>
@@ -20600,7 +20666,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>76</v>
       </c>
@@ -20617,7 +20683,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>76</v>
       </c>
@@ -20634,7 +20700,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>76</v>
       </c>
@@ -20651,7 +20717,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>76</v>
       </c>
@@ -20668,7 +20734,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>76</v>
       </c>
@@ -20685,7 +20751,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>76</v>
       </c>
@@ -20702,7 +20768,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>77</v>
       </c>
@@ -20719,7 +20785,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>77</v>
       </c>
@@ -20736,7 +20802,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>77</v>
       </c>
@@ -20753,7 +20819,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>77</v>
       </c>
@@ -20770,7 +20836,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>77</v>
       </c>
@@ -20787,7 +20853,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>77</v>
       </c>
@@ -20804,7 +20870,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>77</v>
       </c>
@@ -20821,7 +20887,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>77</v>
       </c>
@@ -20838,7 +20904,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>77</v>
       </c>
@@ -20855,7 +20921,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>78</v>
       </c>
@@ -20872,7 +20938,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>78</v>
       </c>
@@ -20889,7 +20955,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>78</v>
       </c>
@@ -20906,7 +20972,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>78</v>
       </c>
@@ -20923,7 +20989,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>78</v>
       </c>
@@ -20940,7 +21006,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>78</v>
       </c>
@@ -20957,7 +21023,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>78</v>
       </c>
@@ -20974,7 +21040,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>78</v>
       </c>
@@ -20991,7 +21057,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>78</v>
       </c>
@@ -21008,7 +21074,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>79</v>
       </c>
@@ -21025,7 +21091,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>79</v>
       </c>
@@ -21042,7 +21108,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>79</v>
       </c>
@@ -21059,7 +21125,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>79</v>
       </c>
@@ -21076,7 +21142,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>79</v>
       </c>
@@ -21093,7 +21159,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>79</v>
       </c>
@@ -21110,7 +21176,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>79</v>
       </c>
@@ -21127,7 +21193,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>79</v>
       </c>
@@ -21144,7 +21210,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>79</v>
       </c>
@@ -21161,7 +21227,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>80</v>
       </c>
@@ -21178,7 +21244,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>80</v>
       </c>
@@ -21195,7 +21261,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>80</v>
       </c>
@@ -21212,7 +21278,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>80</v>
       </c>
@@ -21229,7 +21295,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>80</v>
       </c>
@@ -21246,7 +21312,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>80</v>
       </c>
@@ -21263,7 +21329,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>80</v>
       </c>
@@ -21280,7 +21346,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>80</v>
       </c>
@@ -21297,7 +21363,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>80</v>
       </c>
@@ -21314,7 +21380,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>81</v>
       </c>
@@ -21331,7 +21397,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>81</v>
       </c>
@@ -21348,7 +21414,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>81</v>
       </c>
@@ -21365,7 +21431,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>81</v>
       </c>
@@ -21382,7 +21448,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>81</v>
       </c>
@@ -21399,7 +21465,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>81</v>
       </c>
@@ -21416,7 +21482,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>81</v>
       </c>
@@ -21433,7 +21499,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>81</v>
       </c>
@@ -21450,7 +21516,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>81</v>
       </c>
@@ -21467,7 +21533,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>82</v>
       </c>
@@ -21484,7 +21550,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>82</v>
       </c>
@@ -21501,7 +21567,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>82</v>
       </c>
@@ -21518,7 +21584,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>82</v>
       </c>
@@ -21535,7 +21601,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>82</v>
       </c>
@@ -21552,7 +21618,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>82</v>
       </c>
@@ -21569,7 +21635,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>82</v>
       </c>
@@ -21586,7 +21652,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>82</v>
       </c>
@@ -21603,7 +21669,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>82</v>
       </c>
@@ -21620,7 +21686,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>83</v>
       </c>
@@ -21637,7 +21703,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>83</v>
       </c>
@@ -21654,7 +21720,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>83</v>
       </c>
@@ -21671,7 +21737,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>83</v>
       </c>
@@ -21688,7 +21754,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>83</v>
       </c>
@@ -21705,7 +21771,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>83</v>
       </c>
@@ -21722,7 +21788,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>83</v>
       </c>
@@ -21739,7 +21805,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>83</v>
       </c>
@@ -21756,7 +21822,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>83</v>
       </c>
@@ -21773,7 +21839,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>84</v>
       </c>
@@ -21790,7 +21856,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>84</v>
       </c>
@@ -21807,7 +21873,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742">
         <v>84</v>
       </c>
@@ -21824,7 +21890,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>84</v>
       </c>
@@ -21841,7 +21907,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>84</v>
       </c>
@@ -21858,7 +21924,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>84</v>
       </c>
@@ -21875,7 +21941,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746">
         <v>84</v>
       </c>
@@ -21892,7 +21958,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747">
         <v>84</v>
       </c>
@@ -21909,7 +21975,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748">
         <v>84</v>
       </c>
@@ -21926,7 +21992,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>85</v>
       </c>
@@ -21943,7 +22009,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750">
         <v>85</v>
       </c>
@@ -21960,7 +22026,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>85</v>
       </c>
@@ -21977,7 +22043,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752">
         <v>85</v>
       </c>
@@ -21994,7 +22060,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>85</v>
       </c>
@@ -22011,7 +22077,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>85</v>
       </c>
@@ -22028,7 +22094,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>85</v>
       </c>
@@ -22045,7 +22111,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>85</v>
       </c>
@@ -22062,7 +22128,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>85</v>
       </c>
@@ -22079,7 +22145,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>86</v>
       </c>
@@ -22096,7 +22162,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>86</v>
       </c>
@@ -22113,7 +22179,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760">
         <v>86</v>
       </c>
@@ -22130,7 +22196,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761">
         <v>86</v>
       </c>
@@ -22147,7 +22213,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762">
         <v>86</v>
       </c>
@@ -22164,7 +22230,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763">
         <v>86</v>
       </c>
@@ -22181,7 +22247,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764">
         <v>86</v>
       </c>
@@ -22198,7 +22264,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>86</v>
       </c>
@@ -22215,7 +22281,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766">
         <v>86</v>
       </c>
@@ -22232,7 +22298,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>87</v>
       </c>
@@ -22249,7 +22315,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768">
         <v>87</v>
       </c>
@@ -22266,7 +22332,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>87</v>
       </c>
@@ -22283,7 +22349,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770">
         <v>87</v>
       </c>
@@ -22300,7 +22366,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>87</v>
       </c>
@@ -22317,7 +22383,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772">
         <v>87</v>
       </c>
@@ -22334,7 +22400,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>87</v>
       </c>
@@ -22351,7 +22417,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774">
         <v>87</v>
       </c>
@@ -22368,7 +22434,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>87</v>
       </c>
@@ -22385,7 +22451,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776">
         <v>88</v>
       </c>
@@ -22402,7 +22468,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>88</v>
       </c>
@@ -22419,7 +22485,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778">
         <v>88</v>
       </c>
@@ -22436,7 +22502,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>88</v>
       </c>
@@ -22453,7 +22519,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780">
         <v>88</v>
       </c>
@@ -22470,7 +22536,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>88</v>
       </c>
@@ -22487,7 +22553,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782">
         <v>88</v>
       </c>
@@ -22504,7 +22570,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>88</v>
       </c>
@@ -22521,7 +22587,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784">
         <v>88</v>
       </c>
@@ -22538,7 +22604,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>89</v>
       </c>
@@ -22555,7 +22621,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786">
         <v>89</v>
       </c>
@@ -22572,7 +22638,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787">
         <v>89</v>
       </c>
@@ -22589,7 +22655,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788">
         <v>89</v>
       </c>
@@ -22606,7 +22672,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>89</v>
       </c>
@@ -22623,7 +22689,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790">
         <v>89</v>
       </c>
@@ -22640,7 +22706,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>89</v>
       </c>
@@ -22657,7 +22723,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792">
         <v>89</v>
       </c>
@@ -22674,7 +22740,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>89</v>
       </c>
@@ -22691,7 +22757,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794">
         <v>90</v>
       </c>
@@ -22708,7 +22774,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>90</v>
       </c>
@@ -22725,7 +22791,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796">
         <v>90</v>
       </c>
@@ -22742,7 +22808,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>90</v>
       </c>
@@ -22759,7 +22825,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798">
         <v>90</v>
       </c>
@@ -22776,7 +22842,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>90</v>
       </c>
@@ -22793,7 +22859,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800">
         <v>90</v>
       </c>
@@ -22810,7 +22876,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>90</v>
       </c>
@@ -22827,7 +22893,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802">
         <v>90</v>
       </c>
@@ -22844,7 +22910,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>91</v>
       </c>
@@ -22861,7 +22927,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804">
         <v>91</v>
       </c>
@@ -22878,7 +22944,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>91</v>
       </c>
@@ -22895,7 +22961,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806">
         <v>91</v>
       </c>
@@ -22912,7 +22978,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807">
         <v>91</v>
       </c>
@@ -22929,7 +22995,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808">
         <v>91</v>
       </c>
@@ -22946,7 +23012,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809">
         <v>91</v>
       </c>
@@ -22963,7 +23029,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810">
         <v>91</v>
       </c>
@@ -22980,7 +23046,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811">
         <v>91</v>
       </c>
@@ -22997,7 +23063,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812">
         <v>92</v>
       </c>
@@ -23014,7 +23080,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813">
         <v>92</v>
       </c>
@@ -23031,7 +23097,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814">
         <v>92</v>
       </c>
@@ -23048,7 +23114,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815">
         <v>92</v>
       </c>
@@ -23065,7 +23131,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816">
         <v>92</v>
       </c>
@@ -23082,7 +23148,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817">
         <v>92</v>
       </c>
@@ -23099,7 +23165,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818">
         <v>92</v>
       </c>
@@ -23116,7 +23182,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819">
         <v>92</v>
       </c>
@@ -23133,7 +23199,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820">
         <v>92</v>
       </c>
@@ -23150,7 +23216,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821">
         <v>93</v>
       </c>
@@ -23167,7 +23233,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822">
         <v>93</v>
       </c>
@@ -23184,7 +23250,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823">
         <v>93</v>
       </c>
@@ -23201,7 +23267,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824">
         <v>93</v>
       </c>
@@ -23218,7 +23284,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>93</v>
       </c>
@@ -23235,7 +23301,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826">
         <v>93</v>
       </c>
@@ -23252,7 +23318,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827">
         <v>93</v>
       </c>
@@ -23269,7 +23335,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828">
         <v>93</v>
       </c>
@@ -23286,7 +23352,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>93</v>
       </c>
@@ -23303,7 +23369,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830">
         <v>94</v>
       </c>
@@ -23320,7 +23386,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831">
         <v>94</v>
       </c>
@@ -23337,7 +23403,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832">
         <v>94</v>
       </c>
@@ -23354,7 +23420,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833">
         <v>94</v>
       </c>
@@ -23371,7 +23437,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834">
         <v>94</v>
       </c>
@@ -23388,7 +23454,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835">
         <v>94</v>
       </c>
@@ -23405,7 +23471,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836">
         <v>94</v>
       </c>
@@ -23422,7 +23488,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837">
         <v>94</v>
       </c>
@@ -23439,7 +23505,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838">
         <v>94</v>
       </c>
@@ -23456,7 +23522,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839">
         <v>95</v>
       </c>
@@ -23473,7 +23539,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840">
         <v>95</v>
       </c>
@@ -23490,7 +23556,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841">
         <v>95</v>
       </c>
@@ -23507,7 +23573,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842">
         <v>95</v>
       </c>
@@ -23524,7 +23590,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843">
         <v>95</v>
       </c>
@@ -23541,7 +23607,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844">
         <v>95</v>
       </c>
@@ -23558,7 +23624,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845">
         <v>95</v>
       </c>
@@ -23575,7 +23641,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846">
         <v>95</v>
       </c>
@@ -23592,7 +23658,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847">
         <v>95</v>
       </c>
@@ -23609,7 +23675,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848">
         <v>96</v>
       </c>
@@ -23626,7 +23692,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849">
         <v>96</v>
       </c>
@@ -23643,7 +23709,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850">
         <v>96</v>
       </c>
@@ -23660,7 +23726,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851">
         <v>96</v>
       </c>
@@ -23677,7 +23743,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852">
         <v>96</v>
       </c>
@@ -23694,7 +23760,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853">
         <v>96</v>
       </c>
@@ -23711,7 +23777,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854">
         <v>96</v>
       </c>
@@ -23728,7 +23794,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855">
         <v>96</v>
       </c>
@@ -23745,7 +23811,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856">
         <v>96</v>
       </c>
@@ -23762,7 +23828,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857">
         <v>97</v>
       </c>
@@ -23779,7 +23845,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858">
         <v>97</v>
       </c>
@@ -23796,7 +23862,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>97</v>
       </c>
@@ -23813,7 +23879,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860">
         <v>97</v>
       </c>
@@ -23830,7 +23896,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861">
         <v>97</v>
       </c>
@@ -23847,7 +23913,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862">
         <v>97</v>
       </c>
@@ -23864,7 +23930,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863">
         <v>97</v>
       </c>
@@ -23881,7 +23947,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864">
         <v>97</v>
       </c>
@@ -23898,7 +23964,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865">
         <v>97</v>
       </c>
@@ -23915,7 +23981,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866">
         <v>98</v>
       </c>
@@ -23932,7 +23998,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>98</v>
       </c>
@@ -23949,7 +24015,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868">
         <v>98</v>
       </c>
@@ -23966,7 +24032,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869">
         <v>98</v>
       </c>
@@ -23983,7 +24049,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870">
         <v>98</v>
       </c>
@@ -24000,7 +24066,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871">
         <v>98</v>
       </c>
@@ -24017,7 +24083,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872">
         <v>98</v>
       </c>
@@ -24034,7 +24100,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873">
         <v>98</v>
       </c>
@@ -24051,7 +24117,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874">
         <v>98</v>
       </c>
@@ -24068,7 +24134,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>99</v>
       </c>
@@ -24085,7 +24151,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876">
         <v>99</v>
       </c>
@@ -24102,7 +24168,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>99</v>
       </c>
@@ -24119,7 +24185,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878">
         <v>99</v>
       </c>
@@ -24136,7 +24202,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879">
         <v>99</v>
       </c>
@@ -24153,7 +24219,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880">
         <v>99</v>
       </c>
@@ -24170,7 +24236,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881">
         <v>99</v>
       </c>
@@ -24187,7 +24253,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882">
         <v>99</v>
       </c>
@@ -24204,7 +24270,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883">
         <v>99</v>
       </c>
@@ -24221,7 +24287,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884">
         <v>100</v>
       </c>
@@ -24238,7 +24304,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>100</v>
       </c>
@@ -24255,7 +24321,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="886" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886">
         <v>100</v>
       </c>
@@ -24272,7 +24338,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887">
         <v>100</v>
       </c>
@@ -24289,7 +24355,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="888" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888">
         <v>100</v>
       </c>
@@ -24306,7 +24372,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="889" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889">
         <v>100</v>
       </c>
@@ -24323,7 +24389,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="890" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890">
         <v>100</v>
       </c>
@@ -24340,7 +24406,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="891" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891">
         <v>100</v>
       </c>
@@ -24357,7 +24423,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="892" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892">
         <v>100</v>
       </c>
@@ -24374,7 +24440,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893">
         <v>101</v>
       </c>
@@ -24391,7 +24457,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="894" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894">
         <v>101</v>
       </c>
@@ -24408,7 +24474,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895">
         <v>101</v>
       </c>
@@ -24425,7 +24491,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="896" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896">
         <v>101</v>
       </c>
@@ -24442,7 +24508,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897">
         <v>101</v>
       </c>
@@ -24459,7 +24525,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="898" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898">
         <v>101</v>
       </c>
@@ -24476,7 +24542,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="899" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899">
         <v>101</v>
       </c>
@@ -24493,7 +24559,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="900" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900">
         <v>101</v>
       </c>
@@ -24510,7 +24576,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="901" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901">
         <v>101</v>
       </c>
